--- a/data/Excel/GuLiStrikeSpellFields.xlsx
+++ b/data/Excel/GuLiStrikeSpellFields.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>id</t>
   </si>
@@ -125,6 +125,66 @@
   </si>
   <si>
     <t>Ship僚机对地轰炸；全局共享AOE基础伤害、半径与时序</t>
+  </si>
+  <si>
+    <t>bPermanent</t>
+  </si>
+  <si>
+    <t>bIndestructible</t>
+  </si>
+  <si>
+    <t>LaneHeightCentimeters</t>
+  </si>
+  <si>
+    <t>AscentSeconds</t>
+  </si>
+  <si>
+    <t>AccelerationSeconds</t>
+  </si>
+  <si>
+    <t>DecelerationSeconds</t>
+  </si>
+  <si>
+    <t>ExitFlashSeconds</t>
+  </si>
+  <si>
+    <t>SpeedMultiplier</t>
+  </si>
+  <si>
+    <t>ExitRadiusCentimeters</t>
+  </si>
+  <si>
+    <t>EnergyMaterial</t>
+  </si>
+  <si>
+    <t>softobject</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/StrongholdTransit/M_TransitEnergy.M_TransitEnergy</t>
+  </si>
+  <si>
+    <t>GateMaterial</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/StrongholdTransit/M_TransitGate.M_TransitGate</t>
+  </si>
+  <si>
+    <t>TrailSystem</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/StrongholdTransit/NS_TransitTrail.NS_TransitTrail</t>
+  </si>
+  <si>
+    <t>FlashSystem</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/FX/StrongholdTransit/NS_TransitFlash.NS_TransitFlash</t>
+  </si>
+  <si>
+    <t>StrongholdGate</t>
+  </si>
+  <si>
+    <t>据点常驻空中运输入口，白模参数可调</t>
   </si>
 </sst>
 </file>
@@ -503,6 +563,45 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -559,6 +658,45 @@
       <c r="R2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -615,6 +753,45 @@
       <c r="R3" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" t="s">
+        <v>23</v>
+      </c>
+      <c r="X3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -952,6 +1129,62 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>2001</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10">
+        <v>4000</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>10000</v>
+      </c>
+      <c r="V10">
+        <v>0.5</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.5</v>
+      </c>
+      <c r="Y10">
+        <v>0.2</v>
+      </c>
+      <c r="Z10">
+        <v>50</v>
+      </c>
+      <c r="AA10">
+        <v>4000</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeSpellFields.xlsx
+++ b/data/Excel/GuLiStrikeSpellFields.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -185,6 +185,12 @@
   </si>
   <si>
     <t>据点常驻空中运输入口，白模参数可调</t>
+  </si>
+  <si>
+    <t>StrongholdTransit</t>
+  </si>
+  <si>
+    <t>工程车点击己方据点即时空中运输配置，无地面法阵；原型参数可调</t>
   </si>
 </sst>
 </file>
@@ -564,42 +570,33 @@
         <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="W1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="X1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Z1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AB1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -659,10 +656,10 @@
         <v>20</v>
       </c>
       <c r="S2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U2" t="s">
         <v>20</v>
@@ -680,21 +677,12 @@
         <v>20</v>
       </c>
       <c r="Z2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="AA2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="AB2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE2" t="s">
         <v>47</v>
       </c>
     </row>
@@ -715,7 +703,7 @@
         <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>23</v>
@@ -781,15 +769,6 @@
         <v>23</v>
       </c>
       <c r="AB3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1134,54 +1113,45 @@
         <v>2001</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10">
-        <v>4000</v>
-      </c>
-      <c r="S10" t="b">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10">
+        <v>10000</v>
+      </c>
+      <c r="T10">
+        <v>0.5</v>
+      </c>
+      <c r="U10">
         <v>1</v>
-      </c>
-      <c r="T10" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10">
-        <v>10000</v>
       </c>
       <c r="V10">
         <v>0.5</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="X10">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="Y10">
-        <v>0.2</v>
-      </c>
-      <c r="Z10">
-        <v>50</v>
-      </c>
-      <c r="AA10">
         <v>4000</v>
       </c>
+      <c r="Z10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>52</v>
+      </c>
       <c r="AB10" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE10" t="s">
         <v>54</v>
       </c>
     </row>

--- a/data/Excel/GuLiStrikeSpellFields.xlsx
+++ b/data/Excel/GuLiStrikeSpellFields.xlsx
@@ -789,7 +789,7 @@
         <v>30</v>
       </c>
       <c r="F4">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
@@ -845,7 +845,7 @@
         <v>30</v>
       </c>
       <c r="F5">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -901,7 +901,7 @@
         <v>31</v>
       </c>
       <c r="F6">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -931,13 +931,13 @@
         <v>0.5</v>
       </c>
       <c r="P6">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="Q6">
         <v>10</v>
       </c>
       <c r="R6">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -957,7 +957,7 @@
         <v>31</v>
       </c>
       <c r="F7">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
@@ -987,13 +987,13 @@
         <v>0.5</v>
       </c>
       <c r="P7">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="Q7">
         <v>10</v>
       </c>
       <c r="R7">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
@@ -1013,7 +1013,7 @@
         <v>31</v>
       </c>
       <c r="F8">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
@@ -1043,13 +1043,13 @@
         <v>0.5</v>
       </c>
       <c r="P8">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="Q8">
         <v>10</v>
       </c>
       <c r="R8">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -1069,7 +1069,7 @@
         <v>31</v>
       </c>
       <c r="F9">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
@@ -1099,13 +1099,13 @@
         <v>0.5</v>
       </c>
       <c r="P9">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="Q9">
         <v>10</v>
       </c>
       <c r="R9">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
@@ -1125,7 +1125,7 @@
         <v>31</v>
       </c>
       <c r="S10">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="T10">
         <v>0.5</v>
@@ -1143,7 +1143,7 @@
         <v>50</v>
       </c>
       <c r="Y10">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="Z10" t="s">
         <v>48</v>

--- a/data/Excel/GuLiStrikeSpellFields.xlsx
+++ b/data/Excel/GuLiStrikeSpellFields.xlsx
@@ -789,7 +789,7 @@
         <v>30</v>
       </c>
       <c r="F4">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>

--- a/data/Excel/GuLiStrikeSpellFields.xlsx
+++ b/data/Excel/GuLiStrikeSpellFields.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>id</t>
   </si>
@@ -191,6 +191,15 @@
   </si>
   <si>
     <t>工程车点击己方据点即时空中运输配置，无地面法阵；原型参数可调</t>
+  </si>
+  <si>
+    <t>EnergyVfxId</t>
+  </si>
+  <si>
+    <t>TrailVfxId</t>
+  </si>
+  <si>
+    <t>FlashVfxId</t>
   </si>
 </sst>
 </file>
@@ -591,13 +600,13 @@
         <v>45</v>
       </c>
       <c r="Z1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="AA1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="AB1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
@@ -677,13 +686,13 @@
         <v>20</v>
       </c>
       <c r="Z2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="AB2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -827,6 +836,15 @@
       <c r="R4" t="s">
         <v>31</v>
       </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -883,6 +901,15 @@
       <c r="R5" t="s">
         <v>31</v>
       </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -939,6 +966,15 @@
       <c r="R6">
         <v>2000</v>
       </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -995,6 +1031,15 @@
       <c r="R7">
         <v>2000</v>
       </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1051,6 +1096,15 @@
       <c r="R8">
         <v>2000</v>
       </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -1107,6 +1161,15 @@
       <c r="R9">
         <v>2000</v>
       </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1145,14 +1208,14 @@
       <c r="Y10">
         <v>800</v>
       </c>
-      <c r="Z10" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>54</v>
+      <c r="Z10">
+        <v>12</v>
+      </c>
+      <c r="AA10">
+        <v>13</v>
+      </c>
+      <c r="AB10">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/Excel/GuLiStrikeSpellFields.xlsx
+++ b/data/Excel/GuLiStrikeSpellFields.xlsx
@@ -798,7 +798,7 @@
         <v>30</v>
       </c>
       <c r="F4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
